--- a/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0001T0006Z000C1N66_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0001T0006Z000C1N66_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>45.56213627549884</v>
+        <v>7.403847144768562</v>
       </c>
       <c r="D2" t="n">
-        <v>45.42297698921027</v>
+        <v>7.381233760746669</v>
       </c>
       <c r="E2" t="n">
-        <v>11.9811097006196</v>
+        <v>1.946930326350686</v>
       </c>
       <c r="F2" t="n">
-        <v>12.48353213647774</v>
+        <v>2.028573972177634</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>29.55428349335916</v>
+        <v>4.802571067670864</v>
       </c>
       <c r="D3" t="n">
-        <v>29.3184974721281</v>
+        <v>4.764255839220816</v>
       </c>
       <c r="E3" t="n">
-        <v>11.9811097006196</v>
+        <v>1.946930326350686</v>
       </c>
       <c r="F3" t="n">
-        <v>12.48353213647774</v>
+        <v>2.028573972177634</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>29.14257003664979</v>
+        <v>4.73566763095559</v>
       </c>
       <c r="D4" t="n">
-        <v>11.18219031008122</v>
+        <v>1.817105925388198</v>
       </c>
       <c r="E4" t="n">
-        <v>11.9811097006196</v>
+        <v>1.946930326350686</v>
       </c>
       <c r="F4" t="n">
-        <v>12.48353213647774</v>
+        <v>2.028573972177634</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>17.481985514886</v>
+        <v>2.840822646168975</v>
       </c>
       <c r="D5" t="n">
-        <v>17.42603070048165</v>
+        <v>2.831729988828268</v>
       </c>
       <c r="E5" t="n">
-        <v>11.9811097006196</v>
+        <v>1.946930326350686</v>
       </c>
       <c r="F5" t="n">
-        <v>12.48353213647774</v>
+        <v>2.028573972177634</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>30.53401093183889</v>
+        <v>4.96177677642382</v>
       </c>
       <c r="D6" t="n">
-        <v>30.34459299421295</v>
+        <v>4.930996361559604</v>
       </c>
       <c r="E6" t="n">
-        <v>11.9811097006196</v>
+        <v>1.946930326350686</v>
       </c>
       <c r="F6" t="n">
-        <v>12.48353213647774</v>
+        <v>2.028573972177634</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>16.88623917249301</v>
+        <v>2.744013865530114</v>
       </c>
       <c r="D7" t="n">
-        <v>17.0073615477429</v>
+        <v>2.763696251508221</v>
       </c>
       <c r="E7" t="n">
-        <v>11.9811097006196</v>
+        <v>1.946930326350686</v>
       </c>
       <c r="F7" t="n">
-        <v>12.48353213647774</v>
+        <v>2.028573972177634</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>10.6494241073522</v>
+        <v>1.730531417444732</v>
       </c>
       <c r="D8" t="n">
-        <v>13.30071122107097</v>
+        <v>2.161365573424033</v>
       </c>
       <c r="E8" t="n">
-        <v>11.9811097006196</v>
+        <v>1.946930326350686</v>
       </c>
       <c r="F8" t="n">
-        <v>12.48353213647774</v>
+        <v>2.028573972177634</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>10.49468336396809</v>
+        <v>1.705386046644814</v>
       </c>
       <c r="D9" t="n">
-        <v>11.40474025903586</v>
+        <v>1.853270292093327</v>
       </c>
       <c r="E9" t="n">
-        <v>11.9811097006196</v>
+        <v>1.946930326350686</v>
       </c>
       <c r="F9" t="n">
-        <v>12.48353213647774</v>
+        <v>2.028573972177634</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>35.48414428875603</v>
+        <v>5.766173446922854</v>
       </c>
       <c r="D10" t="n">
-        <v>35.39152528495029</v>
+        <v>5.751122858804423</v>
       </c>
       <c r="E10" t="n">
-        <v>11.9811097006196</v>
+        <v>1.946930326350686</v>
       </c>
       <c r="F10" t="n">
-        <v>12.48353213647774</v>
+        <v>2.028573972177634</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>21.51902141025388</v>
+        <v>3.496840979166256</v>
       </c>
       <c r="D11" t="n">
-        <v>21.74593854661993</v>
+        <v>3.533715013825738</v>
       </c>
       <c r="E11" t="n">
-        <v>11.9811097006196</v>
+        <v>1.946930326350686</v>
       </c>
       <c r="F11" t="n">
-        <v>12.48353213647774</v>
+        <v>2.028573972177634</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>30.49729233018087</v>
+        <v>4.955810003654391</v>
       </c>
       <c r="D12" t="n">
-        <v>30.7086964375514</v>
+        <v>4.990163171102102</v>
       </c>
       <c r="E12" t="n">
-        <v>11.9811097006196</v>
+        <v>1.946930326350686</v>
       </c>
       <c r="F12" t="n">
-        <v>12.48353213647774</v>
+        <v>2.028573972177634</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>43.71249278118354</v>
+        <v>7.103280076942326</v>
       </c>
       <c r="D13" t="n">
-        <v>43.66334057913821</v>
+        <v>7.095292844109959</v>
       </c>
       <c r="E13" t="n">
-        <v>11.9811097006196</v>
+        <v>1.946930326350686</v>
       </c>
       <c r="F13" t="n">
-        <v>12.48353213647774</v>
+        <v>2.028573972177634</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>48.87664058058071</v>
+        <v>7.942454094344365</v>
       </c>
       <c r="D14" t="n">
-        <v>48.86219750573505</v>
+        <v>7.940107094681947</v>
       </c>
       <c r="E14" t="n">
-        <v>11.9811097006196</v>
+        <v>1.946930326350686</v>
       </c>
       <c r="F14" t="n">
-        <v>12.48353213647774</v>
+        <v>2.028573972177634</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>36.89967655841464</v>
+        <v>5.996197440742379</v>
       </c>
       <c r="D15" t="n">
-        <v>37.07649388479179</v>
+        <v>6.024930256278665</v>
       </c>
       <c r="E15" t="n">
-        <v>11.9811097006196</v>
+        <v>1.946930326350686</v>
       </c>
       <c r="F15" t="n">
-        <v>12.48353213647774</v>
+        <v>2.028573972177634</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
